--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:59</t>
+    <t xml:space="preserve">2026-09-10 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:11</t>
+    <t xml:space="preserve">2026-09-12 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:23</t>
+    <t xml:space="preserve">2026-09-23 23:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:52</t>
+    <t xml:space="preserve">2026-10-02 15:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:53</t>
+    <t xml:space="preserve">2026-10-04 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:34</t>
+    <t xml:space="preserve">2026-10-05 16:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
